--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_infodisplay/lang_infodisplay__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_infodisplay/lang_infodisplay__name_title__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey (1)</t>
+          <t>Khảo sát Sinh thái Rừng Mờ (1)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey (2)</t>
+          <t>Khảo sát Sinh thái Rừng Mờ (2)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey (3)</t>
+          <t>Khảo sát Sinh thái Rừng Mờ (3)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey (4)</t>
+          <t>Khảo sát Sinh thái Rừng Mờ (4)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey (5)</t>
+          <t>Khảo sát Sinh thái Rừng Mờ (5)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dim Forest Ecological Survey (Conclusion)</t>
+          <t>Khảo sát Sinh thái Rừng Mờ (Kết luận)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Map Nơi Ẩn Náu</t>
+          <t>Bản Đồ Nơi Ẩn Náu</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Featured Shows of the Season</t>
+          <t>Chương Trình Nổi Bật Mùa Này</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Work Brief</t>
+          <t>Báo cáo công việc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Knell Garden</t>
+          <t>Vườn Knell</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Giọng nói of Tolling</t>
+          <t>Tiếng Chuông Cảnh Báo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Maintanence Records</t>
+          <t>Hồ Sơ Bảo Trì</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Viewer's Bình luận</t>
+          <t>Bình luận của người xem</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lost and Found</t>
+          <t>Đồ Thất Lạc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Squeaky Delivery Recruitment</t>
+          <t>Tuyển Dụng Nhân Viên Giao Hàng Lách Cách</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Academic Lecture Schedule, Huanglong Academy</t>
+          <t>Lịch Trình Bài Giảng Học Thuật, Học Viện Huanglong</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>夜莺茶馆</t>
+          <t>Quán Trà Nightingale</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Emergency Evacuation Thông báo</t>
+          <t>Thông Báo Sơ Tán Khẩn Cấp</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Package List</t>
+          <t>Danh sách Gói</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ancient Banyan "Longwang"</t>
+          <t>Cổ Thụ "Long Vương"</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Hotel An Dưỡng Tuần ~ Số 100 ~</t>
+          <t>Khách Sạn An Dưỡng Tuần ~ Số 100 ~</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Jiaping's Diary</t>
+          <t>Nhật Ký của Jiaping</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Phân Tích Component Sương Mù Tại Vực Sâu Mù Mịt</t>
+          <t>Phân Tích Thành Phần Sương Mù Tại Vực Sâu Mù Mịt</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>A joke</t>
+          <t>Một trò đùa</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Terminal transcript</t>
+          <t>Bản ghi thiết bị đầu cuối</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Equipment Repair Record</t>
+          <t>Biên Bản Sửa Chữa Trang Bị</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Ghi chú of an engineer</t>
+          <t>Ghi chép của một kỹ sư</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Warning on Wutherium Fluid can</t>
+          <t>Cảnh báo về bình chứa dung dịch Wutherium</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Sound of Stone</t>
+          <t>Âm Thanh Đá</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Business Advertisement for the Port</t>
+          <t>Quảng cáo Thương mại tại Cảng</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Journal làm việc tại Cảng</t>
+          <t>Nhật ký làm việc tại Cảng</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Expressway Bulletin</t>
+          <t>Thông Báo Xa Lộ</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Supply application form template</t>
+          <t>Mẫu đơn xin cấp vật tư</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Exiles' Slogan</t>
+          <t>Khẩu Hiệu Của Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Cemetery of the Lost</t>
+          <t>Nghĩa Trang Của Những Kẻ Lạc Lối</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Incineranur Security Administration</t>
+          <t>Cơ Quan An Ninh Incineranur</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Ji Ting Data Chip</t>
+          <t>Thẻ Dữ Liệu Ji Ting</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Personal Journal</t>
+          <t>Nhật Ký Cá Nhân</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Survey Report</t>
+          <t>Báo cáo khảo sát</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Camp Thông báo</t>
+          <t>Thông báo Trại</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Lab Report for XXX</t>
+          <t>Báo Cáo Thí Nghiệm cho XXX</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>皇龙重建史</t>
+          <t>Lịch sử tái thiết Hoàng Long</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Dumpling Coupon</t>
+          <t>Phiếu Mua Bánh Bao</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>修复中的画作</t>
+          <t>Bức tranh đang được phục chế</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>修复记录</t>
+          <t>Biên bản sửa chữa</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>第171号修复品</t>
+          <t>Vật phẩm sửa chữa số 171</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>第281号修复品</t>
+          <t>Vật phẩm sửa chữa số 281</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>日记一则</t>
+          <t>Một trang nhật ký</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
